--- a/data/trans_orig/P16-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2007</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>178051</t>
+          <t>178527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>222538</t>
+          <t>221417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>147691</t>
+          <t>148944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>182218</t>
+          <t>181273</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>338369</t>
+          <t>338789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>396808</t>
+          <t>392345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251238</t>
+          <t>252359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295725</t>
+          <t>295249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124462</t>
+          <t>125407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158989</t>
+          <t>157736</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>383649</t>
+          <t>388112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>442088</t>
+          <t>441668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,59%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126058</t>
+          <t>125838</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165814</t>
+          <t>165678</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180012</t>
+          <t>179836</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>218706</t>
+          <t>218271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>315544</t>
+          <t>316640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>370731</t>
+          <t>373516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201120</t>
+          <t>201256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>240876</t>
+          <t>241096</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153159</t>
+          <t>153594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>191853</t>
+          <t>192029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368068</t>
+          <t>365283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>423255</t>
+          <t>422159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>198500</t>
+          <t>197499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>245012</t>
+          <t>243896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77525</t>
+          <t>77511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103130</t>
+          <t>104092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284974</t>
+          <t>287037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>339679</t>
+          <t>340412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297377</t>
+          <t>298493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343889</t>
+          <t>344890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64652</t>
+          <t>63690</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90257</t>
+          <t>90271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>370492</t>
+          <t>369759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>425197</t>
+          <t>423134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>523797</t>
+          <t>525688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>594864</t>
+          <t>596246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>359804</t>
+          <t>358383</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>411265</t>
+          <t>409749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>902447</t>
+          <t>898425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>993931</t>
+          <t>988708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>643470</t>
+          <t>642088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>714537</t>
+          <t>712646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>303020</t>
+          <t>304536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354481</t>
+          <t>355902</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>958689</t>
+          <t>963912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1050173</t>
+          <t>1054195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,99%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124278</t>
+          <t>124564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160556</t>
+          <t>160805</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>325557</t>
+          <t>325828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>372529</t>
+          <t>375596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>460909</t>
+          <t>462713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>521806</t>
+          <t>521901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>188981</t>
+          <t>188732</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>225259</t>
+          <t>224973</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196223</t>
+          <t>193156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>243195</t>
+          <t>242924</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>396483</t>
+          <t>396388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>457380</t>
+          <t>455576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>43738</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70604</t>
+          <t>70631</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>753653</t>
+          <t>754251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>822695</t>
+          <t>821253</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>804545</t>
+          <t>809370</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>878940</t>
+          <t>882133</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227597</t>
+          <t>227570</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254679</t>
+          <t>254463</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>426065</t>
+          <t>427507</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>495107</t>
+          <t>494509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>668020</t>
+          <t>664827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>742415</t>
+          <t>737590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1265605</t>
+          <t>1271302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1384678</t>
+          <t>1381394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1918162</t>
+          <t>1925145</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2035458</t>
+          <t>2038986</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3230812</t>
+          <t>3209430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3388591</t>
+          <t>3383241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,9%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1884494</t>
+          <t>1887778</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2003567</t>
+          <t>1997870</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1342666</t>
+          <t>1339138</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1459962</t>
+          <t>1452979</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3258705</t>
+          <t>3264055</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3416484</t>
+          <t>3437866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2012</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2012 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>195164</t>
+          <t>193716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>237810</t>
+          <t>238059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173438</t>
+          <t>173755</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>209111</t>
+          <t>212514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>376091</t>
+          <t>378398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>436472</t>
+          <t>435506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199401</t>
+          <t>199152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>243495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105343</t>
+          <t>101940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141016</t>
+          <t>140699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>315193</t>
+          <t>316159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>375574</t>
+          <t>373267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>185690</t>
+          <t>187692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231213</t>
+          <t>230020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194110</t>
+          <t>196399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231930</t>
+          <t>233037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>393430</t>
+          <t>391447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>453740</t>
+          <t>451297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185805</t>
+          <t>186998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>231328</t>
+          <t>229326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>103997</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142924</t>
+          <t>140635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>300312</t>
+          <t>302755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>360622</t>
+          <t>362605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>324029</t>
+          <t>323546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>374431</t>
+          <t>375153</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155064</t>
+          <t>158840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>187851</t>
+          <t>190931</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>491437</t>
+          <t>496238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>555223</t>
+          <t>552714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>253898</t>
+          <t>253176</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304300</t>
+          <t>304783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72278</t>
+          <t>69198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105065</t>
+          <t>101289</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>333236</t>
+          <t>335745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>397022</t>
+          <t>392221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>573974</t>
+          <t>575729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>644205</t>
+          <t>647852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>490419</t>
+          <t>491432</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>544496</t>
+          <t>544875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1084350</t>
+          <t>1081119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1173932</t>
+          <t>1172737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>513925</t>
+          <t>510278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>584156</t>
+          <t>582401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222161</t>
+          <t>221782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>276238</t>
+          <t>275225</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>750856</t>
+          <t>752051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>840438</t>
+          <t>843669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>236147</t>
+          <t>235142</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>280210</t>
+          <t>280159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>550943</t>
+          <t>552903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>601427</t>
+          <t>602391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>800222</t>
+          <t>796583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>868742</t>
+          <t>866179</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>230386</t>
+          <t>230437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>274449</t>
+          <t>275454</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159060</t>
+          <t>158096</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209544</t>
+          <t>207584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>402342</t>
+          <t>404905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>470862</t>
+          <t>474501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65760</t>
+          <t>67359</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97723</t>
+          <t>96369</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>785811</t>
+          <t>783407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>845289</t>
+          <t>843103</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>857568</t>
+          <t>860891</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>928636</t>
+          <t>930254</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168118</t>
+          <t>169472</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200081</t>
+          <t>198482</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263172</t>
+          <t>265358</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>322650</t>
+          <t>325054</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>445666</t>
+          <t>444048</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516734</t>
+          <t>513411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1664151</t>
+          <t>1656346</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1789781</t>
+          <t>1781671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2435455</t>
+          <t>2434171</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2548377</t>
+          <t>2545599</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4128087</t>
+          <t>4129316</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4291446</t>
+          <t>4293310</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1627344</t>
+          <t>1635454</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1752974</t>
+          <t>1760779</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>998847</t>
+          <t>1001625</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1111769</t>
+          <t>1113053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2672903</t>
+          <t>2671039</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2836262</t>
+          <t>2835033</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2016</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205276</t>
+          <t>202735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249260</t>
+          <t>246588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173629</t>
+          <t>171919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210995</t>
+          <t>209895</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>389423</t>
+          <t>390298</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>448444</t>
+          <t>448534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,79%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>179832</t>
+          <t>182504</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>223816</t>
+          <t>226357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136060</t>
+          <t>137160</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>173426</t>
+          <t>175136</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327703</t>
+          <t>327613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>386724</t>
+          <t>385849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>169651</t>
+          <t>168857</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>209368</t>
+          <t>207977</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187861</t>
+          <t>191529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>228589</t>
+          <t>229322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>373258</t>
+          <t>372149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>426276</t>
+          <t>426456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>167859</t>
+          <t>169250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207576</t>
+          <t>208370</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143684</t>
+          <t>142951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184412</t>
+          <t>180744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>323224</t>
+          <t>323044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376242</t>
+          <t>377351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>270930</t>
+          <t>268355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>314845</t>
+          <t>313796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104944</t>
+          <t>102877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127329</t>
+          <t>126736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>381818</t>
+          <t>382117</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>433616</t>
+          <t>434771</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>207069</t>
+          <t>208118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>250984</t>
+          <t>253559</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38794</t>
+          <t>39387</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61179</t>
+          <t>63246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254420</t>
+          <t>253265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306218</t>
+          <t>305919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>564514</t>
+          <t>562724</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>631064</t>
+          <t>629031</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>455994</t>
+          <t>452398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>510327</t>
+          <t>510758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033348</t>
+          <t>1032865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1122081</t>
+          <t>1124031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>518574</t>
+          <t>520607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>585124</t>
+          <t>586914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315549</t>
+          <t>315118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369882</t>
+          <t>373478</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>853433</t>
+          <t>851483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>942166</t>
+          <t>942649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>285803</t>
+          <t>288633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>339909</t>
+          <t>336328</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>507124</t>
+          <t>507427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>557039</t>
+          <t>554568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>808376</t>
+          <t>810891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>883328</t>
+          <t>882909</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280797</t>
+          <t>284378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334903</t>
+          <t>332073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181205</t>
+          <t>183676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>231120</t>
+          <t>230817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>475622</t>
+          <t>476041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>550574</t>
+          <t>548059</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85518</t>
+          <t>85687</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>725377</t>
+          <t>725437</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>788065</t>
+          <t>785131</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>789546</t>
+          <t>788118</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>867166</t>
+          <t>862951</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,03%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201627</t>
+          <t>201458</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231017</t>
+          <t>230754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>293960</t>
+          <t>296894</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>356648</t>
+          <t>356588</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>502004</t>
+          <t>506219</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>579624</t>
+          <t>581052</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,44%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1629271</t>
+          <t>1628661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1748449</t>
+          <t>1745263</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2230070</t>
+          <t>2224641</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2339965</t>
+          <t>2344618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3896300</t>
+          <t>3896812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4071503</t>
+          <t>4056023</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,64%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1637273</t>
+          <t>1640459</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1756451</t>
+          <t>1757061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1191631</t>
+          <t>1186978</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1301526</t>
+          <t>1306955</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2845815</t>
+          <t>2861295</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3021018</t>
+          <t>3020506</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2023</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>259113</t>
+          <t>258632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>304938</t>
+          <t>306135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>244450</t>
+          <t>243588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>280664</t>
+          <t>280833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>514053</t>
+          <t>510961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>574050</t>
+          <t>570384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,87%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>200274</t>
+          <t>199077</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246099</t>
+          <t>246580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166803</t>
+          <t>166634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203017</t>
+          <t>203879</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378629</t>
+          <t>382295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>438626</t>
+          <t>441718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>223967</t>
+          <t>224902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>270470</t>
+          <t>270446</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206727</t>
+          <t>204016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239747</t>
+          <t>238338</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>441204</t>
+          <t>441505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>498312</t>
+          <t>495835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,4%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181743</t>
+          <t>181767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>228246</t>
+          <t>227311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>142833</t>
+          <t>144242</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175853</t>
+          <t>178564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>336481</t>
+          <t>338958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>393589</t>
+          <t>393288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91394</t>
+          <t>99811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>397934</t>
+          <t>398979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113103</t>
+          <t>113006</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131679</t>
+          <t>131286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159448</t>
+          <t>173002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>533030</t>
+          <t>527722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270330</t>
+          <t>269285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>576870</t>
+          <t>568453</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35232</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>53905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>302145</t>
+          <t>307453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675727</t>
+          <t>662173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>536747</t>
+          <t>534021</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>606651</t>
+          <t>607613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>603660</t>
+          <t>602884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>825807</t>
+          <t>810858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1154967</t>
+          <t>1159505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1466873</t>
+          <t>1500961</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>428168</t>
+          <t>427206</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>498072</t>
+          <t>500798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152287</t>
+          <t>167236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>374434</t>
+          <t>375210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>546039</t>
+          <t>511951</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>857945</t>
+          <t>853407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>239956</t>
+          <t>239460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>286118</t>
+          <t>289631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>526642</t>
+          <t>526781</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>645143</t>
+          <t>650755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>786709</t>
+          <t>793144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>927061</t>
+          <t>930923</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>188928</t>
+          <t>185415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>235090</t>
+          <t>235586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193853</t>
+          <t>188241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>312354</t>
+          <t>312215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386980</t>
+          <t>383118</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>527332</t>
+          <t>520897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42219</t>
+          <t>43396</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90843</t>
+          <t>92439</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>451494</t>
+          <t>448983</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>504946</t>
+          <t>503036</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>500056</t>
+          <t>500016</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>579115</t>
+          <t>577402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149664</t>
+          <t>148068</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198288</t>
+          <t>197111</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>255206</t>
+          <t>257116</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>308658</t>
+          <t>311169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>421544</t>
+          <t>423257</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500603</t>
+          <t>500643</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1283454</t>
+          <t>1328503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1822196</t>
+          <t>1820298</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2260529</t>
+          <t>2270639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2604887</t>
+          <t>2585264</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3591701</t>
+          <t>3594169</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4295853</t>
+          <t>4281786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1553864</t>
+          <t>1555762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2092606</t>
+          <t>2047557</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>969312</t>
+          <t>988935</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1313670</t>
+          <t>1303560</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2654407</t>
+          <t>2668474</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3358559</t>
+          <t>3356091</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>178527</t>
+          <t>179935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>221417</t>
+          <t>223485</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148944</t>
+          <t>147605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181273</t>
+          <t>183792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>338789</t>
+          <t>339214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>392345</t>
+          <t>396333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252359</t>
+          <t>250291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295249</t>
+          <t>293841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125407</t>
+          <t>122888</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157736</t>
+          <t>159075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>388112</t>
+          <t>384124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>441668</t>
+          <t>441243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125838</t>
+          <t>127575</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165678</t>
+          <t>164760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179836</t>
+          <t>180113</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>218271</t>
+          <t>216061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>316640</t>
+          <t>315459</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>373516</t>
+          <t>370776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201256</t>
+          <t>202174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>241096</t>
+          <t>239359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153594</t>
+          <t>155804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192029</t>
+          <t>191752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>365283</t>
+          <t>368023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422159</t>
+          <t>423340</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>197499</t>
+          <t>198731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>243896</t>
+          <t>246192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77511</t>
+          <t>78630</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104092</t>
+          <t>103730</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287037</t>
+          <t>284505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340412</t>
+          <t>335484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298493</t>
+          <t>296197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>344890</t>
+          <t>343658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63690</t>
+          <t>64052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90271</t>
+          <t>89152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>369759</t>
+          <t>374687</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>423134</t>
+          <t>425666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>525688</t>
+          <t>522767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>596246</t>
+          <t>592225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>358383</t>
+          <t>357155</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>409749</t>
+          <t>410173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>898425</t>
+          <t>898526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>988708</t>
+          <t>985912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>642088</t>
+          <t>646109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>712646</t>
+          <t>715567</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>304536</t>
+          <t>304112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>355902</t>
+          <t>357130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>963912</t>
+          <t>966708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1054195</t>
+          <t>1054094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124564</t>
+          <t>124173</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160805</t>
+          <t>161524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>325828</t>
+          <t>327261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>375596</t>
+          <t>373600</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>462713</t>
+          <t>464800</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>521901</t>
+          <t>526732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>188732</t>
+          <t>188013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>224973</t>
+          <t>225364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193156</t>
+          <t>195152</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>242924</t>
+          <t>241491</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>396388</t>
+          <t>391557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>455576</t>
+          <t>453489</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43738</t>
+          <t>42572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70631</t>
+          <t>68011</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>754251</t>
+          <t>754734</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>821253</t>
+          <t>821388</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>809370</t>
+          <t>803286</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>882133</t>
+          <t>882054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227570</t>
+          <t>230190</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254463</t>
+          <t>255629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>427507</t>
+          <t>427372</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>494509</t>
+          <t>494026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>664827</t>
+          <t>664906</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>737590</t>
+          <t>743674</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1271302</t>
+          <t>1270497</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1381394</t>
+          <t>1384179</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1925145</t>
+          <t>1921799</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2038986</t>
+          <t>2033280</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3209430</t>
+          <t>3225686</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3383241</t>
+          <t>3393279</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1887778</t>
+          <t>1884993</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1997870</t>
+          <t>1998675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1339138</t>
+          <t>1344844</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1452979</t>
+          <t>1456325</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3264055</t>
+          <t>3254017</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3437866</t>
+          <t>3421610</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>193716</t>
+          <t>193236</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>238059</t>
+          <t>236952</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173755</t>
+          <t>174164</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>212514</t>
+          <t>209488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>378398</t>
+          <t>378885</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>435506</t>
+          <t>435295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,91%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199152</t>
+          <t>200259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243495</t>
+          <t>243975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101940</t>
+          <t>104966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140699</t>
+          <t>140290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>316159</t>
+          <t>316370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>373267</t>
+          <t>372780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>187692</t>
+          <t>186044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230020</t>
+          <t>230920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196399</t>
+          <t>195001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233037</t>
+          <t>233195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>391447</t>
+          <t>394411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>451297</t>
+          <t>453908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186998</t>
+          <t>186098</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>229326</t>
+          <t>230974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103997</t>
+          <t>103839</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140635</t>
+          <t>142033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>302755</t>
+          <t>300144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>362605</t>
+          <t>359641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>323546</t>
+          <t>323433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>375153</t>
+          <t>375223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158840</t>
+          <t>158992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190931</t>
+          <t>190604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496238</t>
+          <t>493808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>552714</t>
+          <t>551604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,09%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>253176</t>
+          <t>253106</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304783</t>
+          <t>304896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69198</t>
+          <t>69525</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101289</t>
+          <t>101137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>335745</t>
+          <t>336855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>392221</t>
+          <t>394651</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,42%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>575729</t>
+          <t>574781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>647852</t>
+          <t>646509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>491432</t>
+          <t>490578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>544875</t>
+          <t>546388</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1081119</t>
+          <t>1080318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1172737</t>
+          <t>1174246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>510278</t>
+          <t>511621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>582401</t>
+          <t>583349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221782</t>
+          <t>220269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>275225</t>
+          <t>276079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>752051</t>
+          <t>750542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>843669</t>
+          <t>844470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>235142</t>
+          <t>233710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>280159</t>
+          <t>279380</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>552903</t>
+          <t>551846</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>602391</t>
+          <t>599801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>796583</t>
+          <t>800165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>866179</t>
+          <t>865036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>230437</t>
+          <t>231216</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>275454</t>
+          <t>276886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158096</t>
+          <t>160686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207584</t>
+          <t>208641</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>404905</t>
+          <t>406048</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>474501</t>
+          <t>470919</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67359</t>
+          <t>67226</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96369</t>
+          <t>97117</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>783407</t>
+          <t>784485</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>843103</t>
+          <t>844001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>860891</t>
+          <t>858146</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>930254</t>
+          <t>931313</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169472</t>
+          <t>168724</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198482</t>
+          <t>198615</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265358</t>
+          <t>264460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325054</t>
+          <t>323976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>444048</t>
+          <t>442989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513411</t>
+          <t>516156</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1656346</t>
+          <t>1661565</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1781671</t>
+          <t>1777914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2434171</t>
+          <t>2434869</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2545599</t>
+          <t>2546009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4129316</t>
+          <t>4128617</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4293310</t>
+          <t>4294477</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1635454</t>
+          <t>1639211</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1760779</t>
+          <t>1755560</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1001625</t>
+          <t>1001215</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1113053</t>
+          <t>1112355</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2671039</t>
+          <t>2669872</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2835033</t>
+          <t>2835732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>202735</t>
+          <t>205582</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>246588</t>
+          <t>249148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>171919</t>
+          <t>174482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>209895</t>
+          <t>210599</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>390298</t>
+          <t>387811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>448534</t>
+          <t>447875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182504</t>
+          <t>179944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>226357</t>
+          <t>223510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137160</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>175136</t>
+          <t>172573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327613</t>
+          <t>328272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>385849</t>
+          <t>388336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>50,03%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168857</t>
+          <t>168465</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>207977</t>
+          <t>208561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>191529</t>
+          <t>190083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229322</t>
+          <t>229670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372149</t>
+          <t>371576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>426456</t>
+          <t>425069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,71%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169250</t>
+          <t>168666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208370</t>
+          <t>208762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>142951</t>
+          <t>142603</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180744</t>
+          <t>182190</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>323044</t>
+          <t>324431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>377351</t>
+          <t>377924</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>268355</t>
+          <t>266850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>313796</t>
+          <t>312616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102877</t>
+          <t>103645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126736</t>
+          <t>127471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>382117</t>
+          <t>379696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>434771</t>
+          <t>433014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,93%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208118</t>
+          <t>209298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253559</t>
+          <t>255064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39387</t>
+          <t>38652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63246</t>
+          <t>62478</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>253265</t>
+          <t>255022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>305919</t>
+          <t>308340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>562724</t>
+          <t>564787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>629031</t>
+          <t>631103</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>452398</t>
+          <t>452363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>510758</t>
+          <t>509917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1032865</t>
+          <t>1036689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1124031</t>
+          <t>1126710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,03%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>520607</t>
+          <t>518535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>586914</t>
+          <t>584851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315118</t>
+          <t>315959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>373478</t>
+          <t>373513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>851483</t>
+          <t>848804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>942649</t>
+          <t>938825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>288633</t>
+          <t>289779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>336328</t>
+          <t>337283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>507427</t>
+          <t>508007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>554568</t>
+          <t>554522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>810891</t>
+          <t>814827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>882909</t>
+          <t>883233</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,99%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>284378</t>
+          <t>283423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>332073</t>
+          <t>330927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183676</t>
+          <t>183722</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>230817</t>
+          <t>230237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>476041</t>
+          <t>475717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>548059</t>
+          <t>544123</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>56004</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85687</t>
+          <t>86633</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>725437</t>
+          <t>722628</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>785131</t>
+          <t>785532</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>788118</t>
+          <t>789511</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>862951</t>
+          <t>864974</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201458</t>
+          <t>200512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230754</t>
+          <t>231141</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>296894</t>
+          <t>296493</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>356588</t>
+          <t>359397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>506219</t>
+          <t>504196</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>581052</t>
+          <t>579659</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1628661</t>
+          <t>1624753</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1745263</t>
+          <t>1743172</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2224641</t>
+          <t>2231122</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2344618</t>
+          <t>2346508</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3896812</t>
+          <t>3890639</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4056023</t>
+          <t>4057488</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1640459</t>
+          <t>1642550</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1757061</t>
+          <t>1760969</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1186978</t>
+          <t>1185088</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1306955</t>
+          <t>1300474</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2861295</t>
+          <t>2859830</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3020506</t>
+          <t>3026679</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>281075</t>
+          <t>303119</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>258632</t>
+          <t>280567</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>306135</t>
+          <t>326579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>261879</t>
+          <t>282667</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>243588</t>
+          <t>262557</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>280833</t>
+          <t>300732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>542954</t>
+          <t>585786</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>510961</t>
+          <t>554838</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>570384</t>
+          <t>617665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>224137</t>
+          <t>247499</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199077</t>
+          <t>224039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246580</t>
+          <t>270051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>185588</t>
+          <t>205744</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166634</t>
+          <t>187679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203879</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>409725</t>
+          <t>453243</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>382295</t>
+          <t>421364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>441718</t>
+          <t>484191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>247223</t>
+          <t>260540</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>224902</t>
+          <t>235049</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>270446</t>
+          <t>283122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,27 +9011,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>222928</t>
+          <t>244331</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204016</t>
+          <t>228338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>238338</t>
+          <t>263617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>470151</t>
+          <t>504871</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>441505</t>
+          <t>475871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>495835</t>
+          <t>534603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>204990</t>
+          <t>222672</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181767</t>
+          <t>200090</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227311</t>
+          <t>248163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,22 +9124,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>159652</t>
+          <t>178812</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144242</t>
+          <t>159526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178564</t>
+          <t>194805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>364642</t>
+          <t>401484</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>338958</t>
+          <t>371752</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>393288</t>
+          <t>430484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>245448</t>
+          <t>269607</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99811</t>
+          <t>248112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>398979</t>
+          <t>290779</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>122554</t>
+          <t>136189</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113006</t>
+          <t>125674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131286</t>
+          <t>146177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>368002</t>
+          <t>405797</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173002</t>
+          <t>382301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>527722</t>
+          <t>430848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>65,37%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>422816</t>
+          <t>202005</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269285</t>
+          <t>180833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>568453</t>
+          <t>223500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44357</t>
+          <t>51308</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>41320</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53905</t>
+          <t>61823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>467173</t>
+          <t>253312</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307453</t>
+          <t>228261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662173</t>
+          <t>276808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>570263</t>
+          <t>626825</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>534021</t>
+          <t>590269</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>607613</t>
+          <t>665278</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>690226</t>
+          <t>540595</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>602884</t>
+          <t>516627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>810858</t>
+          <t>565707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1260489</t>
+          <t>1167420</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1159505</t>
+          <t>1124098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1500961</t>
+          <t>1211099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>464556</t>
+          <t>505018</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>427206</t>
+          <t>466565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>500798</t>
+          <t>541574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>287868</t>
+          <t>320616</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>167236</t>
+          <t>295504</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>375210</t>
+          <t>344584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>752423</t>
+          <t>825634</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>511951</t>
+          <t>781955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>853407</t>
+          <t>868956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>263456</t>
+          <t>287128</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>239460</t>
+          <t>260576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>289631</t>
+          <t>311783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>596349</t>
+          <t>576864</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>526781</t>
+          <t>552039</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>650755</t>
+          <t>600281</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>859804</t>
+          <t>863992</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>793144</t>
+          <t>827018</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>930923</t>
+          <t>898941</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>211590</t>
+          <t>280836</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185415</t>
+          <t>256181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>235586</t>
+          <t>307388</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>242647</t>
+          <t>253263</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188241</t>
+          <t>229846</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>312215</t>
+          <t>278088</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>454237</t>
+          <t>534099</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383118</t>
+          <t>499150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>520897</t>
+          <t>571073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>63832</t>
+          <t>60408</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43396</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92439</t>
+          <t>83462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>477623</t>
+          <t>524448</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>448983</t>
+          <t>495625</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>503036</t>
+          <t>555507</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>541454</t>
+          <t>584856</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>500016</t>
+          <t>547722</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>577402</t>
+          <t>626455</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>176675</t>
+          <t>176820</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148068</t>
+          <t>153766</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197111</t>
+          <t>196151</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>282529</t>
+          <t>318545</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257116</t>
+          <t>287486</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>311169</t>
+          <t>347368</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>459205</t>
+          <t>495365</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>423257</t>
+          <t>453766</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500643</t>
+          <t>532499</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,3%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1671297</t>
+          <t>1807626</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1328503</t>
+          <t>1743035</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1820298</t>
+          <t>1872077</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2371557</t>
+          <t>2305095</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2270639</t>
+          <t>2255486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2585264</t>
+          <t>2358297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4042855</t>
+          <t>4112721</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3594169</t>
+          <t>4021621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4281786</t>
+          <t>4198093</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>59,33%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1704763</t>
+          <t>1634850</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1555762</t>
+          <t>1570399</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2047557</t>
+          <t>1699441</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1202642</t>
+          <t>1328287</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>988935</t>
+          <t>1275085</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1303560</t>
+          <t>1377896</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2907405</t>
+          <t>2963137</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2668474</t>
+          <t>2877765</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3356091</t>
+          <t>3054237</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3574199</t>
+          <t>3633382</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3574199</t>
+          <t>3633382</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3574199</t>
+          <t>3633382</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6950260</t>
+          <t>7075858</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6950260</t>
+          <t>7075858</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6950260</t>
+          <t>7075858</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
